--- a/SupervisorMobility.API/DataAccess/Templates/Sequence Template.xlsx
+++ b/SupervisorMobility.API/DataAccess/Templates/Sequence Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77304a4152b67e63/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ituriel\OneDrive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9B4CE6B1-7BCB-49C8-AE1E-209E7CAE7E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFCA49CD-AD3A-42B6-8C89-89E7A0D87BFB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4702FE20-D161-42A8-94EE-58D4338A2A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1956" windowWidth="21576" windowHeight="8880" xr2:uid="{2133A3B6-9D6D-4252-8A18-602D069582A2}"/>
+    <workbookView xWindow="52125" yWindow="6255" windowWidth="24825" windowHeight="12240" xr2:uid="{2133A3B6-9D6D-4252-8A18-602D069582A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sequence A" sheetId="1" r:id="rId1"/>
@@ -854,9 +854,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -903,205 +900,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1139,6 +941,204 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1155,10 +1155,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1499,285 +1495,292 @@
   <sheetData>
     <row r="4" spans="2:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:16" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
     </row>
     <row r="6" spans="2:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="43" t="s">
+      <c r="C6" s="96"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="25"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="24"/>
     </row>
     <row r="7" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="46" t="s">
+      <c r="B7" s="97"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="24"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="23"/>
     </row>
     <row r="8" spans="2:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="42"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="79"/>
       <c r="F8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="73" t="s">
+      <c r="G8" s="14"/>
+      <c r="H8" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="74"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="57"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="44"/>
     </row>
     <row r="9" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90"/>
-      <c r="M9" s="91"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="58"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="45"/>
     </row>
     <row r="10" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="59"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="46"/>
     </row>
     <row r="11" spans="2:16" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="84" t="s">
+      <c r="C11" s="84"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="80" t="s">
+      <c r="I11" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="81"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="23"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="22"/>
     </row>
     <row r="12" spans="2:16" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="82" t="s">
+      <c r="C12" s="87"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="83"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="22"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="21"/>
     </row>
     <row r="13" spans="2:16" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="2:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="60" t="s">
+      <c r="B14" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="68" t="s">
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="68"/>
-      <c r="J14" s="62" t="s">
+      <c r="I14" s="26"/>
+      <c r="J14" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="63"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="71" t="s">
+      <c r="K14" s="50"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N14" s="68"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="72"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="57"/>
     </row>
     <row r="15" spans="2:16" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="61"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="7" t="s">
+      <c r="B15" s="48"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="65"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="70"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="56"/>
     </row>
     <row r="16" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="12"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="94"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="105"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="39"/>
     </row>
     <row r="17" spans="2:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="9"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="6"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="106"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="40"/>
     </row>
     <row r="18" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="99" t="s">
+      <c r="B18" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="100"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="101"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="35"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="102"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="104"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="38"/>
     </row>
     <row r="19" spans="2:12" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="8"/>
-      <c r="F19" s="10"/>
+      <c r="B19" s="7"/>
+      <c r="F19" s="9"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="2:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="68"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="13" t="s">
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="93" t="s">
+      <c r="F20" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="93" t="s">
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="14" t="s">
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="13" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:G7"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D12:G12"/>
     <mergeCell ref="N8:N10"/>
     <mergeCell ref="O8:O10"/>
     <mergeCell ref="P8:P10"/>
@@ -1794,22 +1797,15 @@
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:G7"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SupervisorMobility.API/DataAccess/Templates/Sequence Template.xlsx
+++ b/SupervisorMobility.API/DataAccess/Templates/Sequence Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ituriel\OneDrive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\job\Supervisor app\Server\SupervisorMobility.API\DataAccess\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4702FE20-D161-42A8-94EE-58D4338A2A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3718FEDD-FE67-469E-AA64-E65E897FC148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52125" yWindow="6255" windowWidth="24825" windowHeight="12240" xr2:uid="{2133A3B6-9D6D-4252-8A18-602D069582A2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2133A3B6-9D6D-4252-8A18-602D069582A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sequence A" sheetId="1" r:id="rId1"/>
@@ -900,6 +900,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -910,19 +913,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -936,12 +939,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1137,8 +1134,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1495,245 +1495,245 @@
   <sheetData>
     <row r="4" spans="2:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:16" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
     </row>
     <row r="6" spans="2:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="95" t="s">
+      <c r="B6" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="96"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="102" t="s">
+      <c r="C6" s="95"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="103"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="93"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="92"/>
       <c r="N6" s="16"/>
       <c r="O6" s="15"/>
       <c r="P6" s="24"/>
     </row>
     <row r="7" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="97"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="105" t="s">
+      <c r="B7" s="96"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="85"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="88"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="87"/>
       <c r="N7" s="14"/>
       <c r="O7" s="17"/>
       <c r="P7" s="23"/>
     </row>
     <row r="8" spans="2:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="84"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="79"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="78"/>
       <c r="F8" s="4" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="73"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="44"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="43"/>
     </row>
     <row r="9" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="84"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="75"/>
-      <c r="M9" s="76"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="45"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="44"/>
     </row>
     <row r="10" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="46"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="45"/>
     </row>
     <row r="11" spans="2:16" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="84"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="69" t="s">
+      <c r="C11" s="83"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="65" t="s">
+      <c r="I11" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="66"/>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="80"/>
       <c r="N11" s="18"/>
       <c r="O11" s="20"/>
       <c r="P11" s="22"/>
     </row>
     <row r="12" spans="2:16" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="87"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="67" t="s">
+      <c r="C12" s="86"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="68"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
       <c r="N12" s="19"/>
       <c r="O12" s="19"/>
       <c r="P12" s="21"/>
     </row>
     <row r="13" spans="2:16" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="2:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="26" t="s">
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="26"/>
-      <c r="J14" s="49" t="s">
+      <c r="I14" s="27"/>
+      <c r="J14" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="50"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="25" t="s">
+      <c r="K14" s="49"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="57"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="56"/>
     </row>
     <row r="15" spans="2:16" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="48"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="54"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="53"/>
       <c r="H15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="52"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="56"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="55"/>
     </row>
     <row r="16" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="30"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="39"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="105"/>
     </row>
     <row r="17" spans="2:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
       <c r="H17" s="5"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="40"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="106"/>
     </row>
     <row r="18" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="36"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="38"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="39"/>
     </row>
     <row r="19" spans="2:12" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="7"/>
@@ -1741,24 +1741,24 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="2:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
       <c r="E20" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="27" t="s">
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
       <c r="L20" s="13" t="s">
         <v>26</v>
       </c>
